--- a/buildwise_web/BuildWise_BOQ_Report.xlsx
+++ b/buildwise_web/BuildWise_BOQ_Report.xlsx
@@ -32,9 +32,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-    <numFmt numFmtId="60" formatCode="&quot;₹&quot;#,##0.00"/>
+    <numFmt numFmtId="60" formatCode="#,##0.##"/>
+    <numFmt numFmtId="61" formatCode="&quot;₹&quot;#,##0.00"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -67,8 +68,8 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="60" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="61" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -400,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F36"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="48.83203125" customWidth="1"/>
@@ -417,7 +418,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Project: 2-Bedroom-Home-Plan-With-Dimensions | Date: 7/25/2026</v>
+        <v>Project: Villa Horizon Test | Date: 2/8/2026</v>
       </c>
     </row>
     <row r="4">
@@ -442,7 +443,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>A. EARTHWORK</v>
+        <v>1. EARTHWORK &amp; FOUNDATIONS</v>
       </c>
     </row>
     <row r="6">
@@ -450,7 +451,7 @@
         <v>1</v>
       </c>
       <c r="B6" t="str">
-        <v>Excavation in ordinary soil for foundations</v>
+        <v>Earthwork Excavation for columns &amp; foundation pits</v>
       </c>
       <c r="C6" t="str">
         <v>m³</v>
@@ -466,28 +467,28 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="str">
-        <v>B. RCC &amp; STRUCTURAL WORKS</v>
+      <c r="A7">
+        <v>2</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Backfilling and soil compaction with selected earth</v>
+      </c>
+      <c r="C7" t="str">
+        <v>m³</v>
+      </c>
+      <c r="D7" s="1">
+        <v>38.25</v>
+      </c>
+      <c r="E7" s="2">
+        <v>120</v>
+      </c>
+      <c r="F7" s="2">
+        <f>D7*E7</f>
       </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>2</v>
-      </c>
-      <c r="B8" t="str">
-        <v>RCC M20 grade concrete frames</v>
-      </c>
-      <c r="C8" t="str">
-        <v>m³</v>
-      </c>
-      <c r="D8" s="1">
-        <v>38.5</v>
-      </c>
-      <c r="E8" s="2">
-        <v>6200</v>
-      </c>
-      <c r="F8" s="2">
-        <f>D8*E8</f>
+      <c r="A8" t="str">
+        <v>2. STRUCTURAL RCC (REINFORCED CONCRETE)</v>
       </c>
     </row>
     <row r="9">
@@ -495,64 +496,64 @@
         <v>3</v>
       </c>
       <c r="B9" t="str">
-        <v>Steel reinforcement Fe500 TMT bars</v>
+        <v>RCC frame structures - Concrete (M20 Grade)</v>
       </c>
       <c r="C9" t="str">
-        <v>kg</v>
+        <v>m³</v>
       </c>
       <c r="D9" s="1">
-        <v>3270</v>
+        <v>38.5</v>
       </c>
       <c r="E9" s="2">
-        <v>78</v>
+        <v>5500</v>
       </c>
       <c r="F9" s="2">
         <f>D9*E9</f>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="str">
-        <v>C. MASONRY &amp; MATERIALS</v>
+      <c r="A10">
+        <v>4</v>
+      </c>
+      <c r="B10" t="str">
+        <v>TMT steel reinforcement bars (Fe500 Grade)</v>
+      </c>
+      <c r="C10" t="str">
+        <v>kg</v>
+      </c>
+      <c r="D10" s="1">
+        <v>3270</v>
+      </c>
+      <c r="E10" s="2">
+        <v>75</v>
+      </c>
+      <c r="F10" s="2">
+        <f>D10*E10</f>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B11" t="str">
-        <v>Masonry wall units (Standard Red Clay Brick)</v>
+        <v>Centering and shuttering (Formwork for slabs, columns &amp; beams)</v>
       </c>
       <c r="C11" t="str">
-        <v>nos</v>
+        <v>m²</v>
       </c>
       <c r="D11" s="1">
-        <v>14500</v>
+        <v>173.25</v>
       </c>
       <c r="E11" s="2">
-        <v>10</v>
+        <v>380</v>
       </c>
       <c r="F11" s="2">
         <f>D11*E11</f>
       </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>5</v>
-      </c>
-      <c r="B12" t="str">
-        <v>Cement (UltraTech Cement)</v>
-      </c>
-      <c r="C12" t="str">
-        <v>bags</v>
-      </c>
-      <c r="D12" s="1">
-        <v>340</v>
-      </c>
-      <c r="E12" s="2">
-        <v>430</v>
-      </c>
-      <c r="F12" s="2">
-        <f>D12*E12</f>
+      <c r="A12" t="str">
+        <v>3. MASONRY &amp; WALL CONSTRUCTION</v>
       </c>
     </row>
     <row r="13">
@@ -560,16 +561,16 @@
         <v>6</v>
       </c>
       <c r="B13" t="str">
-        <v>River sand / M-Sand (River Sand)</v>
+        <v>Clay brick masonry in CM 1:6 wall structures</v>
       </c>
       <c r="C13" t="str">
-        <v>m³</v>
+        <v>nos</v>
       </c>
       <c r="D13" s="1">
-        <v>24.5</v>
+        <v>14500</v>
       </c>
       <c r="E13" s="2">
-        <v>1400</v>
+        <v>10</v>
       </c>
       <c r="F13" s="2">
         <f>D13*E13</f>
@@ -580,64 +581,64 @@
         <v>7</v>
       </c>
       <c r="B14" t="str">
-        <v>Crushed stone aggregate 20mm (20 mm Aggregate)</v>
+        <v>Cement (OPC 53 Grade) for mortar mix</v>
       </c>
       <c r="C14" t="str">
-        <v>m³</v>
+        <v>bags</v>
       </c>
       <c r="D14" s="1">
-        <v>32</v>
+        <v>340</v>
       </c>
       <c r="E14" s="2">
-        <v>1600</v>
+        <v>430</v>
       </c>
       <c r="F14" s="2">
         <f>D14*E14</f>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="str">
-        <v>D. FINISHING WORKS</v>
+      <c r="A15">
+        <v>8</v>
+      </c>
+      <c r="B15" t="str">
+        <v>River sand / Manufactured sand (M-Sand)</v>
+      </c>
+      <c r="C15" t="str">
+        <v>m³</v>
+      </c>
+      <c r="D15" s="1">
+        <v>24.5</v>
+      </c>
+      <c r="E15" s="2">
+        <v>1400</v>
+      </c>
+      <c r="F15" s="2">
+        <f>D15*E15</f>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B16" t="str">
-        <v>Cement plaster 12mm thick CM 1:4</v>
+        <v>Crushed stone aggregate 20mm</v>
       </c>
       <c r="C16" t="str">
-        <v>m²</v>
+        <v>m³</v>
       </c>
       <c r="D16" s="1">
-        <v>480</v>
+        <v>32</v>
       </c>
       <c r="E16" s="2">
-        <v>300</v>
+        <v>1600</v>
       </c>
       <c r="F16" s="2">
         <f>D16*E16</f>
       </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>9</v>
-      </c>
-      <c r="B17" t="str">
-        <v>Interior emulsion wall painting (Asian Paints)</v>
-      </c>
-      <c r="C17" t="str">
-        <v>m²</v>
-      </c>
-      <c r="D17" s="1">
-        <v>580</v>
-      </c>
-      <c r="E17" s="2">
-        <v>135</v>
-      </c>
-      <c r="F17" s="2">
-        <f>D17*E17</f>
+      <c r="A17" t="str">
+        <v>4. FINISHING &amp; PLASTERING WORKS</v>
       </c>
     </row>
     <row r="18">
@@ -645,16 +646,16 @@
         <v>10</v>
       </c>
       <c r="B18" t="str">
-        <v>Vitrified floor tiles 600x600mm (Kajaria)</v>
+        <v>Cement plastering 12mm thick CM 1:4 internal walls</v>
       </c>
       <c r="C18" t="str">
         <v>m²</v>
       </c>
       <c r="D18" s="1">
-        <v>61</v>
+        <v>480</v>
       </c>
       <c r="E18" s="2">
-        <v>650</v>
+        <v>280</v>
       </c>
       <c r="F18" s="2">
         <f>D18*E18</f>
@@ -665,101 +666,233 @@
         <v>11</v>
       </c>
       <c r="B19" t="str">
-        <v>Liquid membrane waterproofing</v>
+        <v>Emulsion interior wall painting (2 coats over 1 coat primer)</v>
       </c>
       <c r="C19" t="str">
         <v>m²</v>
       </c>
       <c r="D19" s="1">
-        <v>75</v>
+        <v>580</v>
       </c>
       <c r="E19" s="2">
-        <v>380</v>
+        <v>120</v>
       </c>
       <c r="F19" s="2">
         <f>D19*E19</f>
       </c>
     </row>
+    <row r="20">
+      <c r="A20">
+        <v>12</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Vitrified floor tiles (600mm × 600mm) including base mortar</v>
+      </c>
+      <c r="C20" t="str">
+        <v>m²</v>
+      </c>
+      <c r="D20" s="1">
+        <v>61</v>
+      </c>
+      <c r="E20" s="2">
+        <v>650</v>
+      </c>
+      <c r="F20" s="2">
+        <f>D20*E20</f>
+      </c>
+    </row>
     <row r="21">
-      <c r="A21" t="str">
-        <v>BOQ SUMMARY BREAKDOWN</v>
+      <c r="A21">
+        <v>13</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Liquid membrane waterproofing for bathrooms &amp; roof slabs</v>
+      </c>
+      <c r="C21" t="str">
+        <v>m²</v>
+      </c>
+      <c r="D21" s="1">
+        <v>75</v>
+      </c>
+      <c r="E21" s="2">
+        <v>380</v>
+      </c>
+      <c r="F21" s="2">
+        <f>D21*E21</f>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Material Takeoff Cost</v>
-      </c>
-      <c r="F22" s="2">
-        <f>SUM(F6:F19)</f>
+        <v>5. DOORS, WINDOWS &amp; OPENINGS</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="str">
-        <v>Labour Takeoff Cost</v>
+      <c r="A23">
+        <v>14</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Wooden flush doors with frames and standard hardware fittings</v>
+      </c>
+      <c r="C23" t="str">
+        <v>nos</v>
+      </c>
+      <c r="D23" s="1">
+        <v>4</v>
+      </c>
+      <c r="E23" s="2">
+        <v>8500</v>
       </c>
       <c r="F23" s="2">
-        <v>330000</v>
+        <f>D23*E23</f>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="str">
-        <v>Machinery &amp; Rental Equipment</v>
+      <c r="A24">
+        <v>15</v>
+      </c>
+      <c r="B24" t="str">
+        <v>UPVC sliding window frames with 5mm clear float glass</v>
+      </c>
+      <c r="C24" t="str">
+        <v>nos</v>
+      </c>
+      <c r="D24" s="1">
+        <v>6</v>
+      </c>
+      <c r="E24" s="2">
+        <v>6200</v>
       </c>
       <c r="F24" s="2">
-        <v>55000</v>
+        <f>D24*E24</f>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
+        <v>6. ELECTRICAL &amp; PLUMBING LINES</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>16</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Concealed PVC conduit wiring with modular switches &amp; MCBs</v>
+      </c>
+      <c r="C26" t="str">
+        <v>point</v>
+      </c>
+      <c r="D26" s="1">
+        <v>4</v>
+      </c>
+      <c r="E26" s="2">
+        <v>3200</v>
+      </c>
+      <c r="F26" s="2">
+        <f>D26*E26</f>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>17</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Internal plumbing lines (CPVC water inlet &amp; PVC drainage pipes)</v>
+      </c>
+      <c r="C27" t="str">
+        <v>job</v>
+      </c>
+      <c r="D27" s="1">
+        <v>2</v>
+      </c>
+      <c r="E27" s="2">
+        <v>24000</v>
+      </c>
+      <c r="F27" s="2">
+        <f>D27*E27</f>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>BOQ SUMMARY BREAKDOWN</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>Material Takeoff Cost</v>
+      </c>
+      <c r="F30" s="2">
+        <f>SUM(F6:F27)</f>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>Labour Takeoff Cost</v>
+      </c>
+      <c r="F31" s="2">
+        <v>316050</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>Machinery &amp; Rental Equipment</v>
+      </c>
+      <c r="F32" s="2">
+        <v>14200</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
         <v>Overhead &amp; Contractor Margin</v>
       </c>
-      <c r="F25" s="2">
-        <v>155000</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="str">
+      <c r="F33" s="2">
+        <v>151428</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
         <v>Contingency Buffer</v>
       </c>
-      <c r="F26" s="2">
-        <v>77000</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="str">
+      <c r="F34" s="2">
+        <v>77345</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
         <v>GST (18% applied)</v>
       </c>
-      <c r="F27" s="2">
-        <f>SUM(F22:F26)*0.18</f>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="str">
+      <c r="F35" s="2">
+        <f>SUM(F30:F34)*0.18</f>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
         <v>GRAND TOTAL CONTRACT AMOUNT</v>
       </c>
-      <c r="F28" s="2">
-        <f>SUM(F22:F27)</f>
+      <c r="F36" s="2">
+        <f>SUM(F30:F35)</f>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="16">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="A15:F15"/>
-    <mergeCell ref="A21:F21"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="A23:E23"/>
-    <mergeCell ref="A24:E24"/>
-    <mergeCell ref="A25:E25"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A27:E27"/>
-    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A25:F25"/>
+    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A36:E36"/>
   </mergeCells>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F28"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F36"/>
   </ignoredErrors>
 </worksheet>
 </file>